--- a/artfynd/A 12425-2024 artfynd.xlsx
+++ b/artfynd/A 12425-2024 artfynd.xlsx
@@ -4554,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117658692</v>
+        <v>117658639</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>416470</v>
+        <v>416249</v>
       </c>
       <c r="R39" t="n">
-        <v>7045365</v>
+        <v>7045458</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,6 +4630,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4656,7 +4661,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117658639</v>
+        <v>117658642</v>
       </c>
       <c r="B40" t="n">
         <v>57287</v>
@@ -4696,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416249</v>
+        <v>416250</v>
       </c>
       <c r="R40" t="n">
-        <v>7045458</v>
+        <v>7045473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4736,7 +4741,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4763,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117658642</v>
+        <v>117658692</v>
       </c>
       <c r="B41" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,21 +4784,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4803,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416250</v>
+        <v>416470</v>
       </c>
       <c r="R41" t="n">
-        <v>7045473</v>
+        <v>7045365</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4839,11 +4844,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6022,7 +6022,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117658678</v>
+        <v>117658658</v>
       </c>
       <c r="B53" t="n">
         <v>57287</v>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416264</v>
+        <v>416268</v>
       </c>
       <c r="R53" t="n">
-        <v>7045280</v>
+        <v>7045307</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska på 2 granar</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6129,7 +6129,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117658658</v>
+        <v>117658678</v>
       </c>
       <c r="B54" t="n">
         <v>57287</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416268</v>
+        <v>416264</v>
       </c>
       <c r="R54" t="n">
-        <v>7045307</v>
+        <v>7045280</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska på 2 granar</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 12425-2024 artfynd.xlsx
+++ b/artfynd/A 12425-2024 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117658699</v>
+        <v>117658658</v>
       </c>
       <c r="B34" t="n">
-        <v>86816</v>
+        <v>57287</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>416258</v>
+        <v>416268</v>
       </c>
       <c r="R34" t="n">
-        <v>7045325</v>
+        <v>7045307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,6 +4110,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4136,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117658621</v>
+        <v>117658655</v>
       </c>
       <c r="B35" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4176,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>416407</v>
+        <v>416266</v>
       </c>
       <c r="R35" t="n">
-        <v>7044767</v>
+        <v>7045308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4212,6 +4217,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,10 +4248,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117658684</v>
+        <v>117658620</v>
       </c>
       <c r="B36" t="n">
-        <v>90517</v>
+        <v>90499</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,21 +4264,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4278,10 +4288,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>416296</v>
+        <v>416283</v>
       </c>
       <c r="R36" t="n">
-        <v>7044780</v>
+        <v>7045283</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4340,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117658645</v>
+        <v>117658696</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>86816</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,21 +4366,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416176</v>
+        <v>416187</v>
       </c>
       <c r="R37" t="n">
-        <v>7045450</v>
+        <v>7045452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4416,11 +4426,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4447,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117658648</v>
+        <v>117658684</v>
       </c>
       <c r="B38" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,21 +4468,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,10 +4492,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416254</v>
+        <v>416296</v>
       </c>
       <c r="R38" t="n">
-        <v>7045409</v>
+        <v>7044780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4523,11 +4528,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,7 +4554,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117658639</v>
+        <v>117658645</v>
       </c>
       <c r="B39" t="n">
         <v>57287</v>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>416249</v>
+        <v>416176</v>
       </c>
       <c r="R39" t="n">
-        <v>7045458</v>
+        <v>7045450</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117658642</v>
+        <v>117658621</v>
       </c>
       <c r="B40" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416250</v>
+        <v>416407</v>
       </c>
       <c r="R40" t="n">
-        <v>7045473</v>
+        <v>7044767</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,11 +4737,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4768,10 +4763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117658692</v>
+        <v>117658671</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4780,25 +4775,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4808,10 +4803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416470</v>
+        <v>416323</v>
       </c>
       <c r="R41" t="n">
-        <v>7045365</v>
+        <v>7045274</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,7 +4865,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117658664</v>
+        <v>117658642</v>
       </c>
       <c r="B42" t="n">
         <v>57287</v>
@@ -4910,10 +4905,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416266</v>
+        <v>416250</v>
       </c>
       <c r="R42" t="n">
-        <v>7045148</v>
+        <v>7045473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117658655</v>
+        <v>117658691</v>
       </c>
       <c r="B43" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,21 +4988,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5017,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416266</v>
+        <v>416393</v>
       </c>
       <c r="R43" t="n">
-        <v>7045308</v>
+        <v>7045035</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5057,7 +5052,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5084,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117658690</v>
+        <v>117658661</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,21 +5095,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>416328</v>
+        <v>416264</v>
       </c>
       <c r="R44" t="n">
-        <v>7045092</v>
+        <v>7045282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5164,7 +5159,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5191,7 +5186,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117658661</v>
+        <v>117658651</v>
       </c>
       <c r="B45" t="n">
         <v>57287</v>
@@ -5231,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416264</v>
+        <v>416266</v>
       </c>
       <c r="R45" t="n">
-        <v>7045282</v>
+        <v>7045403</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5298,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117658671</v>
+        <v>117658692</v>
       </c>
       <c r="B46" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5310,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5338,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416323</v>
+        <v>416470</v>
       </c>
       <c r="R46" t="n">
-        <v>7045274</v>
+        <v>7045365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117658620</v>
+        <v>117658648</v>
       </c>
       <c r="B47" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5416,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>416283</v>
+        <v>416254</v>
       </c>
       <c r="R47" t="n">
-        <v>7045283</v>
+        <v>7045409</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5476,6 +5471,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117658697</v>
+        <v>117658682</v>
       </c>
       <c r="B48" t="n">
-        <v>86816</v>
+        <v>90495</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,21 +5518,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>416273</v>
+        <v>416433</v>
       </c>
       <c r="R48" t="n">
-        <v>7045398</v>
+        <v>7045134</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117658696</v>
+        <v>117658697</v>
       </c>
       <c r="B49" t="n">
         <v>86816</v>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416187</v>
+        <v>416273</v>
       </c>
       <c r="R49" t="n">
-        <v>7045452</v>
+        <v>7045398</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5706,10 +5706,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117658651</v>
+        <v>117658699</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>86816</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416266</v>
+        <v>416258</v>
       </c>
       <c r="R50" t="n">
-        <v>7045403</v>
+        <v>7045325</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,11 +5782,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5813,10 +5808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117658682</v>
+        <v>117658690</v>
       </c>
       <c r="B51" t="n">
-        <v>90495</v>
+        <v>78480</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5829,21 +5824,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5853,10 +5848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416433</v>
+        <v>416328</v>
       </c>
       <c r="R51" t="n">
-        <v>7045134</v>
+        <v>7045092</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5889,6 +5884,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5915,10 +5915,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117658691</v>
+        <v>117658678</v>
       </c>
       <c r="B52" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416393</v>
+        <v>416264</v>
       </c>
       <c r="R52" t="n">
-        <v>7045035</v>
+        <v>7045280</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska på 2 granar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6022,7 +6022,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117658658</v>
+        <v>117658639</v>
       </c>
       <c r="B53" t="n">
         <v>57287</v>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416268</v>
+        <v>416249</v>
       </c>
       <c r="R53" t="n">
-        <v>7045307</v>
+        <v>7045458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6129,7 +6129,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117658678</v>
+        <v>117658664</v>
       </c>
       <c r="B54" t="n">
         <v>57287</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416264</v>
+        <v>416266</v>
       </c>
       <c r="R54" t="n">
-        <v>7045280</v>
+        <v>7045148</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska på 2 granar</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 12425-2024 artfynd.xlsx
+++ b/artfynd/A 12425-2024 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117658658</v>
+        <v>117658620</v>
       </c>
       <c r="B34" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4050,21 +4050,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>416268</v>
+        <v>416283</v>
       </c>
       <c r="R34" t="n">
-        <v>7045307</v>
+        <v>7045283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,11 +4110,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4141,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117658655</v>
+        <v>117658664</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,7 +4179,7 @@
         <v>416266</v>
       </c>
       <c r="R35" t="n">
-        <v>7045308</v>
+        <v>7045148</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,7 +4216,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4248,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117658620</v>
+        <v>117658690</v>
       </c>
       <c r="B36" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4259,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>416283</v>
+        <v>416328</v>
       </c>
       <c r="R36" t="n">
-        <v>7045283</v>
+        <v>7045092</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,6 +4319,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117658696</v>
+        <v>117658621</v>
       </c>
       <c r="B37" t="n">
-        <v>86816</v>
+        <v>90501</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>416187</v>
+        <v>416407</v>
       </c>
       <c r="R37" t="n">
-        <v>7045452</v>
+        <v>7044767</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117658684</v>
+        <v>117658697</v>
       </c>
       <c r="B38" t="n">
-        <v>90517</v>
+        <v>86818</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>416296</v>
+        <v>416273</v>
       </c>
       <c r="R38" t="n">
-        <v>7044780</v>
+        <v>7045398</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117658645</v>
+        <v>117658648</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>416176</v>
+        <v>416254</v>
       </c>
       <c r="R39" t="n">
-        <v>7045450</v>
+        <v>7045409</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117658621</v>
+        <v>117658658</v>
       </c>
       <c r="B40" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>416407</v>
+        <v>416268</v>
       </c>
       <c r="R40" t="n">
-        <v>7044767</v>
+        <v>7045307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,6 +4737,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4763,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117658671</v>
+        <v>117658691</v>
       </c>
       <c r="B41" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4775,25 +4780,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4803,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416323</v>
+        <v>416393</v>
       </c>
       <c r="R41" t="n">
-        <v>7045274</v>
+        <v>7045035</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4839,6 +4844,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4865,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117658642</v>
+        <v>117658639</v>
       </c>
       <c r="B42" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4905,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416250</v>
+        <v>416249</v>
       </c>
       <c r="R42" t="n">
-        <v>7045473</v>
+        <v>7045458</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,7 +4955,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117658691</v>
+        <v>117658651</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,21 +4998,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>416393</v>
+        <v>416266</v>
       </c>
       <c r="R43" t="n">
-        <v>7045035</v>
+        <v>7045403</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,7 +5062,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5082,7 +5092,7 @@
         <v>117658661</v>
       </c>
       <c r="B44" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5186,10 +5196,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117658651</v>
+        <v>117658682</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>90497</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,21 +5212,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>416266</v>
+        <v>416433</v>
       </c>
       <c r="R45" t="n">
-        <v>7045403</v>
+        <v>7045134</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,11 +5272,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117658692</v>
+        <v>117658678</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5309,21 +5314,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>416470</v>
+        <v>416264</v>
       </c>
       <c r="R46" t="n">
-        <v>7045365</v>
+        <v>7045280</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5369,6 +5374,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska på 2 granar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5395,10 +5405,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117658648</v>
+        <v>117658642</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5435,10 +5445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>416254</v>
+        <v>416250</v>
       </c>
       <c r="R47" t="n">
-        <v>7045409</v>
+        <v>7045473</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5475,7 +5485,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5502,10 +5512,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117658682</v>
+        <v>117658692</v>
       </c>
       <c r="B48" t="n">
-        <v>90495</v>
+        <v>78482</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,21 +5528,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5552,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>416433</v>
+        <v>416470</v>
       </c>
       <c r="R48" t="n">
-        <v>7045134</v>
+        <v>7045365</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5614,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117658697</v>
+        <v>117658684</v>
       </c>
       <c r="B49" t="n">
-        <v>86816</v>
+        <v>90519</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5620,21 +5630,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5644,10 +5654,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>416273</v>
+        <v>416296</v>
       </c>
       <c r="R49" t="n">
-        <v>7045398</v>
+        <v>7044780</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5706,10 +5716,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117658699</v>
+        <v>117658645</v>
       </c>
       <c r="B50" t="n">
-        <v>86816</v>
+        <v>57288</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5722,21 +5732,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5746,10 +5756,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>416258</v>
+        <v>416176</v>
       </c>
       <c r="R50" t="n">
-        <v>7045325</v>
+        <v>7045450</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5782,6 +5792,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5808,10 +5823,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117658690</v>
+        <v>117658699</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>86818</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5824,21 +5839,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5848,10 +5863,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>416328</v>
+        <v>416258</v>
       </c>
       <c r="R51" t="n">
-        <v>7045092</v>
+        <v>7045325</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5884,11 +5899,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5915,10 +5925,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117658678</v>
+        <v>117658671</v>
       </c>
       <c r="B52" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5927,25 +5937,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5955,10 +5965,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>416264</v>
+        <v>416323</v>
       </c>
       <c r="R52" t="n">
-        <v>7045280</v>
+        <v>7045274</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5991,11 +6001,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska på 2 granar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6022,10 +6027,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117658639</v>
+        <v>117658655</v>
       </c>
       <c r="B53" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6062,10 +6067,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>416249</v>
+        <v>416266</v>
       </c>
       <c r="R53" t="n">
-        <v>7045458</v>
+        <v>7045308</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6102,7 +6107,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6129,10 +6134,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117658664</v>
+        <v>117658696</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>86818</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6145,21 +6150,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6169,10 +6174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>416266</v>
+        <v>416187</v>
       </c>
       <c r="R54" t="n">
-        <v>7045148</v>
+        <v>7045452</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6205,11 +6210,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 12425-2024 artfynd.xlsx
+++ b/artfynd/A 12425-2024 artfynd.xlsx
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117658691</v>
+        <v>117658639</v>
       </c>
       <c r="B41" t="n">
-        <v>78482</v>
+        <v>57288</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>416393</v>
+        <v>416249</v>
       </c>
       <c r="R41" t="n">
-        <v>7045035</v>
+        <v>7045458</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117658639</v>
+        <v>117658691</v>
       </c>
       <c r="B42" t="n">
-        <v>57288</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,21 +4891,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>416249</v>
+        <v>416393</v>
       </c>
       <c r="R42" t="n">
-        <v>7045458</v>
+        <v>7045035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
